--- a/artfynd/A 34782-2024 artfynd.xlsx
+++ b/artfynd/A 34782-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1377,7 +1377,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>112606922</v>
+        <v>112610487</v>
       </c>
       <c r="B8" t="n">
         <v>91032</v>
@@ -1413,14 +1413,14 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Torrivaara, Lu lm</t>
+          <t>Storberget, Lu lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
         <v>798008</v>
       </c>
       <c r="R8" t="n">
-        <v>7413769</v>
+        <v>7413766</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1484,10 +1484,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>112610487</v>
+        <v>112610488</v>
       </c>
       <c r="B9" t="n">
-        <v>91032</v>
+        <v>91076</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1496,25 +1496,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1524,10 +1524,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>798008</v>
+        <v>797968</v>
       </c>
       <c r="R9" t="n">
-        <v>7413766</v>
+        <v>7413711</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1588,434 +1588,6 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>112606923</v>
-      </c>
-      <c r="B10" t="n">
-        <v>91076</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>5449</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Svart taggsvamp</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Phellodon niger</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>Torrivaara, Lu lm</t>
-        </is>
-      </c>
-      <c r="Q10" t="n">
-        <v>797966</v>
-      </c>
-      <c r="R10" t="n">
-        <v>7413716</v>
-      </c>
-      <c r="S10" t="n">
-        <v>10</v>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>Gällivare</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>Lule lappmark</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>Gällivare</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>2022-09-14</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>2022-09-14</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT10" t="inlineStr"/>
-      <c r="AW10" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>112606921</v>
-      </c>
-      <c r="B11" t="n">
-        <v>91076</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>5449</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Svart taggsvamp</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Phellodon niger</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>Torrivaara, Lu lm</t>
-        </is>
-      </c>
-      <c r="Q11" t="n">
-        <v>798007</v>
-      </c>
-      <c r="R11" t="n">
-        <v>7413890</v>
-      </c>
-      <c r="S11" t="n">
-        <v>10</v>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>Gällivare</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>Lule lappmark</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>Gällivare</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>2022-09-14</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>2022-09-14</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT11" t="inlineStr"/>
-      <c r="AW11" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>112610488</v>
-      </c>
-      <c r="B12" t="n">
-        <v>91076</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>5449</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Svart taggsvamp</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>Phellodon niger</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>Storberget, Lu lm</t>
-        </is>
-      </c>
-      <c r="Q12" t="n">
-        <v>797968</v>
-      </c>
-      <c r="R12" t="n">
-        <v>7413711</v>
-      </c>
-      <c r="S12" t="n">
-        <v>10</v>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>Gällivare</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>Lule lappmark</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>Gällivare</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>2022-09-14</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>2022-09-14</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT12" t="inlineStr"/>
-      <c r="AW12" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>112610486</v>
-      </c>
-      <c r="B13" t="n">
-        <v>91076</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>5449</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Svart taggsvamp</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>Phellodon niger</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>Storberget, Lu lm</t>
-        </is>
-      </c>
-      <c r="Q13" t="n">
-        <v>798010</v>
-      </c>
-      <c r="R13" t="n">
-        <v>7413889</v>
-      </c>
-      <c r="S13" t="n">
-        <v>10</v>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>Gällivare</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>Lule lappmark</t>
-        </is>
-      </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>Gällivare</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>2022-09-14</t>
-        </is>
-      </c>
-      <c r="AA13" t="inlineStr">
-        <is>
-          <t>2022-09-14</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD13" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE13" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG13" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT13" t="inlineStr"/>
-      <c r="AW13" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
